--- a/perf_study/plot/perf_gain.xlsx
+++ b/perf_study/plot/perf_gain.xlsx
@@ -14454,7 +14454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14465,20 +14465,15 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>kernel_index</t>
+          <t>ipc_gain_pct</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>ipc_gain_pct</t>
+          <t>read_change_pct</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
-        <is>
-          <t>read_change_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
         <is>
           <t>write_change_pct</t>
         </is>
@@ -14490,25 +14485,14 @@
           <t>backprop-rodinia-2.0-ft</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>-0.001</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>-13.119</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>-82.258</t>
-        </is>
+      <c r="B2" s="1" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>-13.157</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>-82.36</v>
       </c>
     </row>
     <row r="3">
@@ -14517,25 +14501,14 @@
           <t>bfs-rodinia-2.0-ft</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>0.037</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>-32.741</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>-50.000</t>
-        </is>
+      <c r="B3" s="2" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>-55.311</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>-100</v>
       </c>
     </row>
     <row r="4">
@@ -14544,25 +14517,14 @@
           <t>heartwall-rodinia-2.0-ft</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0.456</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-13.225</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-100.000</t>
-        </is>
+      <c r="B4" s="2" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>-13.225</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>-100</v>
       </c>
     </row>
     <row r="5">
@@ -14571,25 +14533,14 @@
           <t>hotspot-rodinia-2.0-ft</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-58.549</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
+      <c r="B5" s="1" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>-58.553</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -14598,25 +14549,14 @@
           <t>lud-rodinia-2.0-ft</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-0.015</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-80.000</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
+      <c r="B6" s="1" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>-100</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -14625,25 +14565,14 @@
           <t>nn-rodinia-2.0-ft</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-0.093</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-36.181</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
+      <c r="B7" s="1" t="n">
+        <v>-0.094</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>-36.255</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -14652,25 +14581,14 @@
           <t>nw-rodinia-2.0-ft</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -14679,25 +14597,14 @@
           <t>pathfinder-rodinia-2.0-ft</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-0.018</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-100.000</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-100.000</t>
-        </is>
+      <c r="B9" s="1" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>-100</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>-100</v>
       </c>
     </row>
     <row r="10">
@@ -14706,25 +14613,14 @@
           <t>srad_v2-rodinia-2.0-ft</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0.154</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-57.161</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-25.330</t>
-        </is>
+      <c r="B10" s="2" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>-77.95399999999999</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>-25.332</v>
       </c>
     </row>
     <row r="11">
@@ -14733,29 +14629,84 @@
           <t>streamcluster-rodinia-2.0-ft</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>AVG</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0.056</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-11.693</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-87.951</t>
+      <c r="B11" s="2" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>-11.694</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>-94.72</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>study</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>IPC (geomean)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GLOBAL_ACC_R fails (geomean)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>GLOBAL_ACC_W fails (geomean)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>base-config</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>60.960</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>1950.799</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>44.344</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>mshr-entries-32</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>60.995 (+0.057%)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>439.309 (-77.481%)</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>7.473 (-83.148%)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C11">
+  <conditionalFormatting sqref="B2:B11">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -14763,7 +14714,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D11">
+  <conditionalFormatting sqref="C2:C11">
     <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -14771,7 +14722,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E11">
+  <conditionalFormatting sqref="D2:D11">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
